--- a/Okta3.xlsx
+++ b/Okta3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45799601-F4C9-40CC-92C2-EAECB3193D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F05182-8A20-44B2-A878-6C95CE83AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="1020" windowWidth="27315" windowHeight="14580" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1020" windowWidth="27315" windowHeight="14580" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pin" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="任意２認証ー第１回目" sheetId="8" r:id="rId8"/>
     <sheet name="任意２認証ー第２回目" sheetId="9" r:id="rId9"/>
     <sheet name="認証のボタン" sheetId="10" r:id="rId10"/>
+    <sheet name="ログインエラー" sheetId="11" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="12" r:id="rId12"/>
+    <sheet name="Sheet3" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -860,6 +863,461 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239498</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>153381</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2E3496D-8363-7903-4970-9E707023C918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9840698" cy="7030431"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>134709</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>143830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88C00613-1C88-4D88-85DA-C4943D51C536}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8143875"/>
+          <a:ext cx="9735909" cy="6839905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>458700</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>134101</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7870A0FF-76AD-D141-FA34-C70DB1E0C9FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10745700" cy="5382376"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>77551</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>10335</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C2C3DE6-7CFD-67E6-EBF0-49F627BD787F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5791200"/>
+          <a:ext cx="9678751" cy="5801535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>372771</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>10410</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33B244D5-AC00-66C4-BB30-2D754B172037}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="12306300"/>
+          <a:ext cx="9288171" cy="6344535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>277412</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>67745</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9314F07F-D0A5-8039-22B0-6D38F19C0C1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="19183350"/>
+          <a:ext cx="8507012" cy="7668695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>315805</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>58067</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{307FB468-FDBA-3E96-876D-1BADEA3815B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="34023300"/>
+          <a:ext cx="10602805" cy="6573167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>252</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>448982</xdr:colOff>
+      <xdr:row>283</xdr:row>
+      <xdr:rowOff>19836</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15385C99-5BD0-711E-4F55-4A979EA915D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="45605700"/>
+          <a:ext cx="9364382" cy="5630061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>289</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>601595</xdr:colOff>
+      <xdr:row>326</xdr:row>
+      <xdr:rowOff>96198</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F332C3EC-C321-FB29-2855-5B2BDCF59482}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="52301775"/>
+          <a:ext cx="10888595" cy="6792273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>515762</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>105749</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B49B254D-9CEA-9D35-6493-EC9E642DAE16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10116962" cy="6982799"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3931,6 +4389,39 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFCEF7A-C8A4-4DDA-87EA-95F3BDCF3A74}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD352C5B-2EDC-47D4-823A-4E3802ECAEF6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CE595E-8C41-4F05-81EE-52B234C6A812}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D062A18-3AEF-4F08-8DC4-DD15E865F6A3}">
   <dimension ref="A1"/>

--- a/Okta3.xlsx
+++ b/Okta3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F05182-8A20-44B2-A878-6C95CE83AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F783C912-4B4F-41E2-95F9-17E1D3D6D8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1020" windowWidth="27315" windowHeight="14580" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1020" windowWidth="27315" windowHeight="14580" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pin" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,10 @@
     <sheet name="任意２認証ー第１回目" sheetId="8" r:id="rId8"/>
     <sheet name="任意２認証ー第２回目" sheetId="9" r:id="rId9"/>
     <sheet name="認証のボタン" sheetId="10" r:id="rId10"/>
-    <sheet name="ログインエラー" sheetId="11" r:id="rId11"/>
-    <sheet name="Sheet2" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet3" sheetId="13" r:id="rId13"/>
+    <sheet name="今回対応→" sheetId="14" r:id="rId11"/>
+    <sheet name="ログインエラー" sheetId="11" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="12" r:id="rId13"/>
+    <sheet name="Sheet3" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1312,6 +1313,138 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="10116962" cy="6982799"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>572920</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>153230</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3325F58B-477B-B0A3-180A-574158E8CC5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7419975"/>
+          <a:ext cx="10174120" cy="5944430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>515762</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>808</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95902C78-7127-C6D6-C163-19B70442D6FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13935075"/>
+          <a:ext cx="10116962" cy="5792008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>296752</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>77246</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A93F787-A40D-D758-8299-B05CDDFDED50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20631150"/>
+          <a:ext cx="10583752" cy="7497221"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4390,6 +4523,16 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47EF5519-BC45-48B6-B745-486759DD6952}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFCEF7A-C8A4-4DDA-87EA-95F3BDCF3A74}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4400,7 +4543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD352C5B-2EDC-47D4-823A-4E3802ECAEF6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4411,7 +4554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CE595E-8C41-4F05-81EE-52B234C6A812}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
